--- a/src/畅星agent架构设计.xlsx
+++ b/src/畅星agent架构设计.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\seki\AI\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\seki\AI\Langchain\SIS_Agent\src\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BF5B3502-AEFE-4A90-84D1-038E7A3579B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCAD198E-7B96-4E23-807A-4B77852B9217}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,7 +17,6 @@
     <sheet name="RAG" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="162913"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -30,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="31">
   <si>
     <r>
       <rPr>
@@ -134,6 +133,54 @@
   </si>
   <si>
     <t>12.agent可操作cli，能自己写简单工具</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>长期记忆</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>已完成</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>评估体系（如用RAGAS评估检索质量）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>学习使用 loguru 或 logging 替换 print</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>学习 astream_events 替代手工状态解析</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>尝试构建多Agent协作（例如一个Agent负责检索，另一个Agent负责验证答案）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>实现 HyDE（假设性文档嵌入）或 Query2Doc</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>添加 Self-RAG 或 CRAG（修正检索）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>RAG进阶技巧</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>部署与运维</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>将Agent封装成FastAPI服务，并提供Dockerfile</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>学习使用 langsmith 或 langfuse 做trace和评估</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1875,72 +1922,129 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="Q3:Q15"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <dimension ref="Q3:W26"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="3" spans="17:17" x14ac:dyDescent="0.2">
+    <row r="3" spans="17:20" x14ac:dyDescent="0.3">
       <c r="Q3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="17:17" x14ac:dyDescent="0.2">
+    <row r="4" spans="17:20" x14ac:dyDescent="0.3">
       <c r="Q4" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="5" spans="17:17" x14ac:dyDescent="0.2">
+      <c r="S4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5" spans="17:20" x14ac:dyDescent="0.3">
       <c r="Q5" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="6" spans="17:17" x14ac:dyDescent="0.2">
+      <c r="S5" t="s">
+        <v>20</v>
+      </c>
+      <c r="T5" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="6" spans="17:20" x14ac:dyDescent="0.3">
       <c r="Q6" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="7" spans="17:17" x14ac:dyDescent="0.2">
+      <c r="S6" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="7" spans="17:20" x14ac:dyDescent="0.3">
       <c r="Q7" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="17:17" x14ac:dyDescent="0.2">
+    <row r="8" spans="17:20" x14ac:dyDescent="0.3">
       <c r="Q8" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="17:17" x14ac:dyDescent="0.2">
+    <row r="9" spans="17:20" x14ac:dyDescent="0.3">
       <c r="Q9" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="17:17" x14ac:dyDescent="0.2">
+    <row r="10" spans="17:20" x14ac:dyDescent="0.3">
       <c r="Q10" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="11" spans="17:17" x14ac:dyDescent="0.2">
+    <row r="11" spans="17:20" x14ac:dyDescent="0.3">
       <c r="Q11" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="12" spans="17:17" x14ac:dyDescent="0.2">
+    <row r="12" spans="17:20" x14ac:dyDescent="0.3">
       <c r="Q12" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="13" spans="17:17" x14ac:dyDescent="0.2">
+    <row r="13" spans="17:20" x14ac:dyDescent="0.3">
       <c r="Q13" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="14" spans="17:17" x14ac:dyDescent="0.2">
+    <row r="14" spans="17:20" x14ac:dyDescent="0.3">
       <c r="Q14" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="15" spans="17:17" x14ac:dyDescent="0.2">
+    <row r="15" spans="17:20" x14ac:dyDescent="0.3">
       <c r="Q15" t="s">
         <v>18</v>
+      </c>
+    </row>
+    <row r="17" spans="22:23" x14ac:dyDescent="0.3">
+      <c r="W17" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="18" spans="22:23" x14ac:dyDescent="0.3">
+      <c r="W18" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="19" spans="22:23" x14ac:dyDescent="0.3">
+      <c r="W19" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="20" spans="22:23" x14ac:dyDescent="0.3">
+      <c r="V20" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="21" spans="22:23" x14ac:dyDescent="0.3">
+      <c r="W21" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="22" spans="22:23" x14ac:dyDescent="0.3">
+      <c r="W22" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="24" spans="22:23" x14ac:dyDescent="0.3">
+      <c r="V24" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="25" spans="22:23" x14ac:dyDescent="0.3">
+      <c r="W25" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="26" spans="22:23" x14ac:dyDescent="0.3">
+      <c r="W26" t="s">
+        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -1954,34 +2058,34 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8A0321E1-1843-4C2D-BE9E-06FCD2D96F01}">
   <dimension ref="D8:D16"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="8" spans="4:4" ht="18.75" x14ac:dyDescent="0.4">
+    <row r="8" spans="4:4" ht="18" x14ac:dyDescent="0.55000000000000004">
       <c r="D8" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="9" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D9" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="10" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D10" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="11" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D11" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="12" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="12" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D12" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="16" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="16" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D16" t="s">
         <v>15</v>
       </c>

--- a/src/畅星agent架构设计.xlsx
+++ b/src/畅星agent架构设计.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\seki\AI\Langchain\SIS_Agent\src\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCAD198E-7B96-4E23-807A-4B77852B9217}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{767D3442-5464-471C-B3A8-AD0E1B257B29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="39">
   <si>
     <r>
       <rPr>
@@ -181,6 +181,38 @@
   </si>
   <si>
     <t>学习使用 langsmith 或 langfuse 做trace和评估</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ToDo List</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.Claude code同款双重验证机制（token消耗+最大循环数）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2.操控CLI的subagent</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3.FastAPI</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4.长期记忆</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>5.RAG评估</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>6.强制打断对话</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>7.多轮对话</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1922,7 +1954,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="Q3:W26"/>
+  <dimension ref="C3:W61"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="3" spans="17:20" x14ac:dyDescent="0.3">
@@ -2045,6 +2077,46 @@
     <row r="26" spans="22:23" x14ac:dyDescent="0.3">
       <c r="W26" t="s">
         <v>30</v>
+      </c>
+    </row>
+    <row r="54" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C54" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="55" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="D55" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="56" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="D56" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="57" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="D57" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="58" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="D58" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="59" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="D59" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="60" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="D60" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="61" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="D61" t="s">
+        <v>38</v>
       </c>
     </row>
   </sheetData>

--- a/src/畅星agent架构设计.xlsx
+++ b/src/畅星agent架构设计.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\seki\AI\Langchain\SIS_Agent\src\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{767D3442-5464-471C-B3A8-AD0E1B257B29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A81C87C-FA12-4349-BA7F-7227663731A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -735,81 +735,6 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>228600</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>101600</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>647700</xdr:colOff>
-      <xdr:row>27</xdr:row>
-      <xdr:rowOff>161925</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="17" name="矩形: 圆角 16">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9D4D6587-F0F1-434E-9A3A-136CD42932D9}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="8115300" y="4625975"/>
-          <a:ext cx="1733550" cy="784225"/>
-        </a:xfrm>
-        <a:prstGeom prst="roundRect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="50000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="en-US" altLang="zh-CN" sz="1200"/>
-            <a:t>Tool3</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="zh-CN" altLang="en-US" sz="1200"/>
-            <a:t>：</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" altLang="zh-CN" sz="1200"/>
-            <a:t>RAG</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="zh-CN" altLang="en-US" sz="1200"/>
-            <a:t>本地知识库检索</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>573087</xdr:colOff>
       <xdr:row>17</xdr:row>
@@ -839,59 +764,6 @@
         <a:xfrm rot="5400000" flipH="1" flipV="1">
           <a:off x="4168775" y="2535238"/>
           <a:ext cx="1143000" cy="3076575"/>
-        </a:xfrm>
-        <a:prstGeom prst="bentConnector3">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>363539</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>63500</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>438151</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>104775</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="20" name="连接符: 肘形 19">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4FD7CF08-1093-4A29-8A4B-9F2A2BC4FC37}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvCxnSpPr>
-          <a:stCxn id="17" idx="0"/>
-          <a:endCxn id="2" idx="2"/>
-        </xdr:cNvCxnSpPr>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm rot="16200000" flipV="1">
-          <a:off x="7066757" y="2713832"/>
-          <a:ext cx="1127125" cy="2703512"/>
         </a:xfrm>
         <a:prstGeom prst="bentConnector3">
           <a:avLst/>
@@ -1252,15 +1124,7 @@
           </a:br>
           <a:r>
             <a:rPr lang="zh-CN" altLang="en-US" sz="1200"/>
-            <a:t>（基于千问</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" altLang="zh-CN" sz="1200"/>
-            <a:t>3.5plus</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="zh-CN" altLang="en-US" sz="1200"/>
-            <a:t>内置工具）</a:t>
+            <a:t>（基于火山引擎搜索工具）</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>
@@ -1320,143 +1184,6 @@
         </a:fontRef>
       </xdr:style>
     </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>438150</xdr:colOff>
-      <xdr:row>27</xdr:row>
-      <xdr:rowOff>158750</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>438150</xdr:colOff>
-      <xdr:row>33</xdr:row>
-      <xdr:rowOff>63501</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="43" name="直接连接符 42">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{65B7ECC0-4F37-4034-836E-7768A77ED396}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvCxnSpPr>
-          <a:stCxn id="17" idx="2"/>
-          <a:endCxn id="46" idx="0"/>
-        </xdr:cNvCxnSpPr>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="8982075" y="5045075"/>
-          <a:ext cx="0" cy="990601"/>
-        </a:xfrm>
-        <a:prstGeom prst="line">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>228600</xdr:colOff>
-      <xdr:row>33</xdr:row>
-      <xdr:rowOff>63501</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>647700</xdr:colOff>
-      <xdr:row>39</xdr:row>
-      <xdr:rowOff>57150</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="46" name="矩形: 圆角 45">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{72B0C359-810C-402F-A7F7-7F02755E8BA6}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="8115300" y="6035676"/>
-          <a:ext cx="1733550" cy="1079499"/>
-        </a:xfrm>
-        <a:prstGeom prst="roundRect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="50000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="zh-CN" altLang="en-US" sz="1200"/>
-            <a:t>分块，召回等算法待优化</a:t>
-          </a:r>
-          <a:endParaRPr lang="en-US" altLang="zh-CN" sz="1200"/>
-        </a:p>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="zh-CN" altLang="en-US" sz="1200"/>
-            <a:t>设想：</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" altLang="zh-CN" sz="1200"/>
-            <a:t>FAQ </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="zh-CN" altLang="en-US" sz="1200"/>
-            <a:t>增强型 </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" altLang="zh-CN" sz="1200"/>
-            <a:t>RAG+rerank</a:t>
-          </a:r>
-          <a:endParaRPr lang="zh-CN" altLang="en-US" sz="1200"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>

--- a/src/畅星agent架构设计.xlsx
+++ b/src/畅星agent架构设计.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\seki\AI\Langchain\SIS_Agent\src\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A81C87C-FA12-4349-BA7F-7227663731A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EEBFDD0-B331-4723-8638-B3823799659D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="40">
   <si>
     <r>
       <rPr>
@@ -215,12 +215,16 @@
     <t>7.多轮对话</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
+  <si>
+    <t>沙箱环境，工具，提示词优化</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -257,6 +261,14 @@
       <charset val="128"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <strike/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -278,9 +290,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1806,42 +1819,45 @@
         <v>30</v>
       </c>
     </row>
-    <row r="54" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="54" spans="3:7" x14ac:dyDescent="0.3">
       <c r="C54" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="55" spans="3:4" x14ac:dyDescent="0.3">
-      <c r="D55" t="s">
+    <row r="55" spans="3:7" x14ac:dyDescent="0.3">
+      <c r="D55" s="2" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="56" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="56" spans="3:7" x14ac:dyDescent="0.3">
       <c r="D56" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="57" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="G56" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="57" spans="3:7" x14ac:dyDescent="0.3">
       <c r="D57" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="58" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="58" spans="3:7" x14ac:dyDescent="0.3">
       <c r="D58" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="59" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="59" spans="3:7" x14ac:dyDescent="0.3">
       <c r="D59" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="60" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="60" spans="3:7" x14ac:dyDescent="0.3">
       <c r="D60" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="61" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="61" spans="3:7" x14ac:dyDescent="0.3">
       <c r="D61" t="s">
         <v>38</v>
       </c>
